--- a/data/v2g_params.xlsx
+++ b/data/v2g_params.xlsx
@@ -4484,7 +4484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:N97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4535,6 +4535,26 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>WkndWinter_Buy_EUR_kWh</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WkndSummer_Buy_EUR_kWh</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>WkndWinter_V2G_EUR_kWh</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>WkndSummer_V2G_EUR_kWh</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
@@ -4569,9 +4589,21 @@
       <c r="I2" t="n">
         <v>0.2038</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J2" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -4605,9 +4637,21 @@
       <c r="I3" t="n">
         <v>0.2038</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J3" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -4641,9 +4685,21 @@
       <c r="I4" t="n">
         <v>0.2038</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J4" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -4677,9 +4733,21 @@
       <c r="I5" t="n">
         <v>0.2038</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J5" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -4713,9 +4781,21 @@
       <c r="I6" t="n">
         <v>0.2038</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J6" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -4749,9 +4829,21 @@
       <c r="I7" t="n">
         <v>0.2038</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J7" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -4785,9 +4877,21 @@
       <c r="I8" t="n">
         <v>0.2038</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J8" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -4821,9 +4925,21 @@
       <c r="I9" t="n">
         <v>0.2038</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J9" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -4857,9 +4973,21 @@
       <c r="I10" t="n">
         <v>0.2038</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J10" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -4893,9 +5021,21 @@
       <c r="I11" t="n">
         <v>0.2038</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J11" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -4929,9 +5069,21 @@
       <c r="I12" t="n">
         <v>0.2038</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J12" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -4965,9 +5117,21 @@
       <c r="I13" t="n">
         <v>0.2038</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J13" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5001,9 +5165,21 @@
       <c r="I14" t="n">
         <v>0.2038</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J14" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5037,9 +5213,21 @@
       <c r="I15" t="n">
         <v>0.2038</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J15" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5073,9 +5261,21 @@
       <c r="I16" t="n">
         <v>0.2038</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J16" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5109,9 +5309,21 @@
       <c r="I17" t="n">
         <v>0.2038</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J17" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5145,9 +5357,21 @@
       <c r="I18" t="n">
         <v>0.2038</v>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J18" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5181,9 +5405,21 @@
       <c r="I19" t="n">
         <v>0.2038</v>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J19" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5217,9 +5453,21 @@
       <c r="I20" t="n">
         <v>0.2038</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J20" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5253,9 +5501,21 @@
       <c r="I21" t="n">
         <v>0.2038</v>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J21" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5289,9 +5549,21 @@
       <c r="I22" t="n">
         <v>0.224</v>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J22" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5325,9 +5597,21 @@
       <c r="I23" t="n">
         <v>0.224</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J23" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5361,9 +5645,21 @@
       <c r="I24" t="n">
         <v>0.224</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J24" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5397,9 +5693,21 @@
       <c r="I25" t="n">
         <v>0.224</v>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J25" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5433,9 +5741,21 @@
       <c r="I26" t="n">
         <v>0.224</v>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J26" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5469,9 +5789,21 @@
       <c r="I27" t="n">
         <v>0.224</v>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J27" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5505,9 +5837,21 @@
       <c r="I28" t="n">
         <v>0.224</v>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J28" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5541,9 +5885,21 @@
       <c r="I29" t="n">
         <v>0.224</v>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J29" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5577,9 +5933,21 @@
       <c r="I30" t="n">
         <v>0.2716</v>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J30" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5613,9 +5981,21 @@
       <c r="I31" t="n">
         <v>0.2716</v>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J31" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5649,9 +6029,21 @@
       <c r="I32" t="n">
         <v>0.2716</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J32" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5685,9 +6077,21 @@
       <c r="I33" t="n">
         <v>0.2716</v>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J33" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5721,9 +6125,21 @@
       <c r="I34" t="n">
         <v>0.2716</v>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J34" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5757,9 +6173,21 @@
       <c r="I35" t="n">
         <v>0.2716</v>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J35" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5793,9 +6221,21 @@
       <c r="I36" t="n">
         <v>0.2716</v>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J36" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5829,9 +6269,21 @@
       <c r="I37" t="n">
         <v>0.2716</v>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J37" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5865,9 +6317,21 @@
       <c r="I38" t="n">
         <v>0.2633</v>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J38" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5901,9 +6365,21 @@
       <c r="I39" t="n">
         <v>0.2633</v>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J39" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5937,9 +6413,21 @@
       <c r="I40" t="n">
         <v>0.2633</v>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J40" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -5973,9 +6461,21 @@
       <c r="I41" t="n">
         <v>0.2633</v>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J41" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6009,9 +6509,21 @@
       <c r="I42" t="n">
         <v>0.2633</v>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J42" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6045,9 +6557,21 @@
       <c r="I43" t="n">
         <v>0.2633</v>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J43" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6081,9 +6605,21 @@
       <c r="I44" t="n">
         <v>0.2633</v>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J44" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6117,9 +6653,21 @@
       <c r="I45" t="n">
         <v>0.2633</v>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J45" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6153,9 +6701,21 @@
       <c r="I46" t="n">
         <v>0.18</v>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J46" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6189,9 +6749,21 @@
       <c r="I47" t="n">
         <v>0.18</v>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J47" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6225,9 +6797,21 @@
       <c r="I48" t="n">
         <v>0.18</v>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J48" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6261,9 +6845,21 @@
       <c r="I49" t="n">
         <v>0.18</v>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J49" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6297,9 +6893,21 @@
       <c r="I50" t="n">
         <v>0.18</v>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J50" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6333,9 +6941,21 @@
       <c r="I51" t="n">
         <v>0.18</v>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J51" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6369,9 +6989,21 @@
       <c r="I52" t="n">
         <v>0.18</v>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J52" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6405,9 +7037,21 @@
       <c r="I53" t="n">
         <v>0.18</v>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J53" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6441,9 +7085,21 @@
       <c r="I54" t="n">
         <v>0.18</v>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J54" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6477,9 +7133,21 @@
       <c r="I55" t="n">
         <v>0.18</v>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J55" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6513,9 +7181,21 @@
       <c r="I56" t="n">
         <v>0.18</v>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J56" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6549,9 +7229,21 @@
       <c r="I57" t="n">
         <v>0.18</v>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J57" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6585,9 +7277,21 @@
       <c r="I58" t="n">
         <v>0.18</v>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J58" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6621,9 +7325,21 @@
       <c r="I59" t="n">
         <v>0.18</v>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J59" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6657,9 +7373,21 @@
       <c r="I60" t="n">
         <v>0.18</v>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J60" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6693,9 +7421,21 @@
       <c r="I61" t="n">
         <v>0.18</v>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J61" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6729,9 +7469,21 @@
       <c r="I62" t="n">
         <v>0.2442</v>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J62" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6765,9 +7517,21 @@
       <c r="I63" t="n">
         <v>0.2442</v>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J63" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6801,9 +7565,21 @@
       <c r="I64" t="n">
         <v>0.2442</v>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J64" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6837,9 +7613,21 @@
       <c r="I65" t="n">
         <v>0.2442</v>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J65" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6868,14 +7656,26 @@
         <v>0.2442</v>
       </c>
       <c r="H66" t="n">
-        <v>0.4738</v>
+        <v>0.3418</v>
       </c>
       <c r="I66" t="n">
         <v>0.2442</v>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J66" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6904,14 +7704,26 @@
         <v>0.2442</v>
       </c>
       <c r="H67" t="n">
-        <v>0.4738</v>
+        <v>0.3418</v>
       </c>
       <c r="I67" t="n">
         <v>0.2442</v>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J67" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6940,14 +7752,26 @@
         <v>0.2442</v>
       </c>
       <c r="H68" t="n">
-        <v>0.4738</v>
+        <v>0.3418</v>
       </c>
       <c r="I68" t="n">
         <v>0.2442</v>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J68" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -6976,14 +7800,26 @@
         <v>0.2442</v>
       </c>
       <c r="H69" t="n">
-        <v>0.4738</v>
+        <v>0.3418</v>
       </c>
       <c r="I69" t="n">
         <v>0.2442</v>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J69" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7012,14 +7848,26 @@
         <v>0.3025</v>
       </c>
       <c r="H70" t="n">
-        <v>0.4738</v>
+        <v>0.3418</v>
       </c>
       <c r="I70" t="n">
-        <v>0.4005</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+        <v>0.3025</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7048,14 +7896,26 @@
         <v>0.3025</v>
       </c>
       <c r="H71" t="n">
-        <v>0.4738</v>
+        <v>0.3418</v>
       </c>
       <c r="I71" t="n">
-        <v>0.4005</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+        <v>0.3025</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7084,14 +7944,26 @@
         <v>0.3025</v>
       </c>
       <c r="H72" t="n">
-        <v>0.4738</v>
+        <v>0.3418</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4005</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+        <v>0.3025</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7120,14 +7992,26 @@
         <v>0.3025</v>
       </c>
       <c r="H73" t="n">
-        <v>0.4738</v>
+        <v>0.3418</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4005</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+        <v>0.3025</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7156,14 +8040,26 @@
         <v>0.3025</v>
       </c>
       <c r="H74" t="n">
-        <v>0.4738</v>
+        <v>0.3418</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4005</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+        <v>0.3025</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7192,14 +8088,26 @@
         <v>0.3025</v>
       </c>
       <c r="H75" t="n">
-        <v>0.4738</v>
+        <v>0.3418</v>
       </c>
       <c r="I75" t="n">
-        <v>0.4005</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+        <v>0.3025</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7228,14 +8136,26 @@
         <v>0.3025</v>
       </c>
       <c r="H76" t="n">
-        <v>0.4738</v>
+        <v>0.3418</v>
       </c>
       <c r="I76" t="n">
-        <v>0.4005</v>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+        <v>0.3025</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7264,14 +8184,26 @@
         <v>0.3025</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4738</v>
+        <v>0.3418</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4005</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+        <v>0.3025</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7300,14 +8232,26 @@
         <v>0.3025</v>
       </c>
       <c r="H78" t="n">
-        <v>0.431</v>
+        <v>0.299</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4005</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+        <v>0.3025</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7336,14 +8280,26 @@
         <v>0.3025</v>
       </c>
       <c r="H79" t="n">
-        <v>0.431</v>
+        <v>0.299</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4005</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+        <v>0.3025</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7372,14 +8328,26 @@
         <v>0.3025</v>
       </c>
       <c r="H80" t="n">
-        <v>0.431</v>
+        <v>0.299</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4005</v>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+        <v>0.3025</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7408,14 +8376,26 @@
         <v>0.3025</v>
       </c>
       <c r="H81" t="n">
-        <v>0.431</v>
+        <v>0.299</v>
       </c>
       <c r="I81" t="n">
-        <v>0.4005</v>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+        <v>0.3025</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7449,9 +8429,21 @@
       <c r="I82" t="n">
         <v>0.2597</v>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J82" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7485,9 +8477,21 @@
       <c r="I83" t="n">
         <v>0.2597</v>
       </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J83" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7521,9 +8525,21 @@
       <c r="I84" t="n">
         <v>0.2597</v>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J84" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7557,9 +8573,21 @@
       <c r="I85" t="n">
         <v>0.2597</v>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J85" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7593,9 +8621,21 @@
       <c r="I86" t="n">
         <v>0.2597</v>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J86" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7629,9 +8669,21 @@
       <c r="I87" t="n">
         <v>0.2597</v>
       </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J87" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7665,9 +8717,21 @@
       <c r="I88" t="n">
         <v>0.2597</v>
       </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J88" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7701,9 +8765,21 @@
       <c r="I89" t="n">
         <v>0.2597</v>
       </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J89" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7737,9 +8813,21 @@
       <c r="I90" t="n">
         <v>0.2085</v>
       </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J90" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7773,9 +8861,21 @@
       <c r="I91" t="n">
         <v>0.2085</v>
       </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J91" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7809,9 +8909,21 @@
       <c r="I92" t="n">
         <v>0.2085</v>
       </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J92" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7845,9 +8957,21 @@
       <c r="I93" t="n">
         <v>0.2085</v>
       </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J93" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7881,9 +9005,21 @@
       <c r="I94" t="n">
         <v>0.2085</v>
       </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J94" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7917,9 +9053,21 @@
       <c r="I95" t="n">
         <v>0.2085</v>
       </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J95" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7953,9 +9101,21 @@
       <c r="I96" t="n">
         <v>0.2085</v>
       </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J96" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
@@ -7989,9 +9149,21 @@
       <c r="I97" t="n">
         <v>0.2085</v>
       </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>EPEX SMARD.de 2024 avg WD by season + BNetzA 2024</t>
+      <c r="J97" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>EPEX SMARD.de 2024 avg by season/daytype + BNetzA 2024</t>
         </is>
       </c>
     </row>
